--- a/downloads/UAS-5_Skor.xlsx
+++ b/downloads/UAS-5_Skor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\projects\Kominter\all-about-me\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894324C4-C801-4753-BC33-229BC48EC465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05969025-BA2E-4D77-BFC8-AD1024687862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="13896" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
   </bookViews>
@@ -751,7 +751,7 @@
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="G7" s="4" t="str">
-        <f t="shared" ref="G3:G66" si="0">IF(COUNT(C7:F7)=0,"",AVERAGE(C7:F7))</f>
+        <f t="shared" ref="G7:G66" si="0">IF(COUNT(C7:F7)=0,"",AVERAGE(C7:F7))</f>
         <v/>
       </c>
       <c r="L7" s="4"/>
